--- a/artfynd/A 56337-2025 artfynd.xlsx
+++ b/artfynd/A 56337-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122093</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136122096</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56337-2025 artfynd.xlsx
+++ b/artfynd/A 56337-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122093</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136122096</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136122089</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136122095</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>136125751</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136125752</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>136122087</v>
       </c>
       <c r="B8" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136122088</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136122090</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136122091</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136122092</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56337-2025 artfynd.xlsx
+++ b/artfynd/A 56337-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122093</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136122096</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136122089</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136122095</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>136125751</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136125752</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>136122087</v>
       </c>
       <c r="B8" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136122088</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136122090</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136122091</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136122092</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56337-2025 artfynd.xlsx
+++ b/artfynd/A 56337-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122093</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136122096</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136122089</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>136122095</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>136125751</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136125752</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>136122087</v>
       </c>
       <c r="B8" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136122088</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136122090</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136122091</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>136122092</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
